--- a/实验设计/语法分析/语法表格/预测分析表.xlsx
+++ b/实验设计/语法分析/语法表格/预测分析表.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="预测分析表" sheetId="1" r:id="R96997a9599fd4a7c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="冲突与处理" sheetId="2" r:id="Rf9ba257627f047a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="终结符" sheetId="3" r:id="R5505831310cb4145"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="语法约束" sheetId="4" r:id="R00baf14b42f64272"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="预测分析表" sheetId="1" r:id="Re3522e7a6a4f4d98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="冲突与处理" sheetId="2" r:id="Rcca8c3cffd214099"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="终结符" sheetId="3" r:id="R7e533d8986d04fb6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="语法约束" sheetId="4" r:id="Ra8d6accc71f54a96"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -7138,7 +7138,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0cebf34f4d3f4f3e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a84c2afc87d4a64"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7223,7 +7223,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6086c5882fc8434a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc511daf3ad3a4fc7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7756,7 +7756,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R28b6fc62c16544cc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd5c74d24041f4278"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7842,7 +7842,7 @@
         <x:v>PARSE_ARRAY_BOUND / 语义</x:v>
       </x:c>
       <x:c r="E8" s="17" t="str">
-        <x:v>src/语法分析/parser.cpp:149</x:v>
+        <x:v>src/语法分析/parser.cpp:94</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="24" customHeight="1">
@@ -7859,7 +7859,7 @@
         <x:v>PARSE_LITERAL / 语义</x:v>
       </x:c>
       <x:c r="E9" s="18" t="str">
-        <x:v>src/语法分析/parser.cpp:409</x:v>
+        <x:v>src/语法分析/parser.cpp:256</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
@@ -7876,7 +7876,7 @@
         <x:v>PARSE_ASSIGNMENT_TARGET / 语义</x:v>
       </x:c>
       <x:c r="E10" s="17" t="str">
-        <x:v>src/语法分析/parser.cpp:390</x:v>
+        <x:v>src/语法分析/parser.cpp:233</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="24" customHeight="1">
@@ -7893,7 +7893,7 @@
         <x:v>语义</x:v>
       </x:c>
       <x:c r="E11" s="18" t="str">
-        <x:v>src/语法分析/parser.cpp:222</x:v>
+        <x:v>src/语法分析/parser.cpp:133</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="24" customHeight="1">
@@ -7910,7 +7910,7 @@
         <x:v>语义</x:v>
       </x:c>
       <x:c r="E12" s="17" t="str">
-        <x:v>src/语法分析/parser.cpp:327</x:v>
+        <x:v>src/语法分析/parser.cpp:203</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
@@ -7927,7 +7927,7 @@
         <x:v>AST</x:v>
       </x:c>
       <x:c r="E13" s="18" t="str">
-        <x:v>src/语法分析/parser.cpp:82</x:v>
+        <x:v>src/语法分析/parser.cpp:74</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="24" customHeight="1">
@@ -7938,13 +7938,13 @@
         <x:v>错误恢复</x:v>
       </x:c>
       <x:c r="C14" s="17" t="str">
-        <x:v>语法错误后跳到分号、块结束或下一个声明开头继续分析；错误输入不交付成功 AST。</x:v>
+        <x:v>按预测项和 FOLLOW 同步；终结符失配时跳过输入或补缺，错误输入不交付成功 AST。</x:v>
       </x:c>
       <x:c r="D14" s="17" t="str">
         <x:v>PARSE_EXPECTED</x:v>
       </x:c>
       <x:c r="E14" s="17" t="str">
-        <x:v>src/语法分析/parser.cpp:283</x:v>
+        <x:v>src/语法分析/parser.cpp:366</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -7953,7 +7953,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa74c51101e44cb7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re16afff522e748f2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/实验设计/语法分析/语法表格/预测分析表.xlsx
+++ b/实验设计/语法分析/语法表格/预测分析表.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="预测分析表" sheetId="1" r:id="Re3522e7a6a4f4d98"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="冲突与处理" sheetId="2" r:id="Rcca8c3cffd214099"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="终结符" sheetId="3" r:id="R7e533d8986d04fb6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="语法约束" sheetId="4" r:id="Ra8d6accc71f54a96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="预测分析表" sheetId="1" r:id="Rc9a309a130df4b39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="冲突与处理" sheetId="2" r:id="R6f36996c937a47e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="终结符" sheetId="3" r:id="R94581404fc0d46a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="语法约束" sheetId="4" r:id="R1b2d080a175246c3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -7138,7 +7138,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a84c2afc87d4a64"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d400a6b91f041a2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7223,7 +7223,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc511daf3ad3a4fc7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7075a6cbf8c4ca4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7756,7 +7756,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd5c74d24041f4278"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a2ecc984d6e451d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7842,7 +7842,7 @@
         <x:v>PARSE_ARRAY_BOUND / 语义</x:v>
       </x:c>
       <x:c r="E8" s="17" t="str">
-        <x:v>src/语法分析/parser.cpp:94</x:v>
+        <x:v>src/语法分析/parser.cpp:93</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="24" customHeight="1">
@@ -7859,7 +7859,7 @@
         <x:v>PARSE_LITERAL / 语义</x:v>
       </x:c>
       <x:c r="E9" s="18" t="str">
-        <x:v>src/语法分析/parser.cpp:256</x:v>
+        <x:v>src/语法分析/parser.cpp:190</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
@@ -7876,7 +7876,7 @@
         <x:v>PARSE_ASSIGNMENT_TARGET / 语义</x:v>
       </x:c>
       <x:c r="E10" s="17" t="str">
-        <x:v>src/语法分析/parser.cpp:233</x:v>
+        <x:v>src/语法分析/parser.cpp:179</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="24" customHeight="1">
@@ -7893,7 +7893,7 @@
         <x:v>语义</x:v>
       </x:c>
       <x:c r="E11" s="18" t="str">
-        <x:v>src/语法分析/parser.cpp:133</x:v>
+        <x:v>src/语法分析/parser.cpp:122</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="24" customHeight="1">
@@ -7910,7 +7910,7 @@
         <x:v>语义</x:v>
       </x:c>
       <x:c r="E12" s="17" t="str">
-        <x:v>src/语法分析/parser.cpp:203</x:v>
+        <x:v>src/语法分析/parser.cpp:153</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
@@ -7927,7 +7927,7 @@
         <x:v>AST</x:v>
       </x:c>
       <x:c r="E13" s="18" t="str">
-        <x:v>src/语法分析/parser.cpp:74</x:v>
+        <x:v>src/语法分析/parser.cpp:67</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="24" customHeight="1">
@@ -7944,7 +7944,7 @@
         <x:v>PARSE_EXPECTED</x:v>
       </x:c>
       <x:c r="E14" s="17" t="str">
-        <x:v>src/语法分析/parser.cpp:366</x:v>
+        <x:v>src/语法分析/parser.cpp:290</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -7953,7 +7953,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re16afff522e748f2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce2828f589964d57"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/实验设计/语法分析/语法表格/预测分析表.xlsx
+++ b/实验设计/语法分析/语法表格/预测分析表.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="预测分析表" sheetId="1" r:id="Rc9a309a130df4b39"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="冲突与处理" sheetId="2" r:id="R6f36996c937a47e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="终结符" sheetId="3" r:id="R94581404fc0d46a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="语法约束" sheetId="4" r:id="R1b2d080a175246c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="预测分析表" sheetId="1" r:id="Ra59a3980c38240c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="冲突与处理" sheetId="2" r:id="R47142ac5143a4910"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="终结符" sheetId="3" r:id="Rcf3f352125a545b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="语法约束" sheetId="4" r:id="R1b7cba995259433e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -7138,7 +7138,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d400a6b91f041a2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40bf1c06c88f4489"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7223,7 +7223,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7075a6cbf8c4ca4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R794da46213824563"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7756,7 +7756,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a2ecc984d6e451d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc14d0e16d3d402a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7842,7 +7842,7 @@
         <x:v>PARSE_ARRAY_BOUND / 语义</x:v>
       </x:c>
       <x:c r="E8" s="17" t="str">
-        <x:v>src/语法分析/parser.cpp:93</x:v>
+        <x:v>src/语法分析/parser.cpp:83</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="24" customHeight="1">
@@ -7859,7 +7859,7 @@
         <x:v>PARSE_LITERAL / 语义</x:v>
       </x:c>
       <x:c r="E9" s="18" t="str">
-        <x:v>src/语法分析/parser.cpp:190</x:v>
+        <x:v>src/语法分析/parser.cpp:180</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
@@ -7876,7 +7876,7 @@
         <x:v>PARSE_ASSIGNMENT_TARGET / 语义</x:v>
       </x:c>
       <x:c r="E10" s="17" t="str">
-        <x:v>src/语法分析/parser.cpp:179</x:v>
+        <x:v>src/语法分析/parser.cpp:169</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="24" customHeight="1">
@@ -7893,7 +7893,7 @@
         <x:v>语义</x:v>
       </x:c>
       <x:c r="E11" s="18" t="str">
-        <x:v>src/语法分析/parser.cpp:122</x:v>
+        <x:v>src/语法分析/parser.cpp:112</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="24" customHeight="1">
@@ -7910,7 +7910,7 @@
         <x:v>语义</x:v>
       </x:c>
       <x:c r="E12" s="17" t="str">
-        <x:v>src/语法分析/parser.cpp:153</x:v>
+        <x:v>src/语法分析/parser.cpp:143</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
@@ -7927,7 +7927,7 @@
         <x:v>AST</x:v>
       </x:c>
       <x:c r="E13" s="18" t="str">
-        <x:v>src/语法分析/parser.cpp:67</x:v>
+        <x:v>src/语法分析/parser.cpp:57</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="24" customHeight="1">
@@ -7935,16 +7935,16 @@
         <x:v>C07</x:v>
       </x:c>
       <x:c r="B14" s="17" t="str">
-        <x:v>错误恢复</x:v>
+        <x:v>首次出错停止</x:v>
       </x:c>
       <x:c r="C14" s="17" t="str">
-        <x:v>按预测项和 FOLLOW 同步；终结符失配时跳过输入或补缺，错误输入不交付成功 AST。</x:v>
+        <x:v>预测表空格或终结符失配时报告第一条错误并立即退出，不交付成功 AST。</x:v>
       </x:c>
       <x:c r="D14" s="17" t="str">
         <x:v>PARSE_EXPECTED</x:v>
       </x:c>
       <x:c r="E14" s="17" t="str">
-        <x:v>src/语法分析/parser.cpp:290</x:v>
+        <x:v>src/语法分析/parser.cpp:280</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -7953,7 +7953,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce2828f589964d57"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3f22222842594b01"/>
   </x:tableParts>
 </x:worksheet>
 </file>